--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104589_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104589_W15.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9576</v>
+        <v>3.3402</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2284</v>
+        <v>2.2362</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7293</v>
+        <v>1.1041</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6157</v>
+        <v>-0.5271</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8716</v>
+        <v>0.2073</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2559</v>
+        <v>-0.7344000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6859</v>
+        <v>2.2656</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1792</v>
+        <v>1.5438</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4932</v>
+        <v>0.7217</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0702</v>
+        <v>-2.7927</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3075</v>
+        <v>-1.3365</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2373</v>
+        <v>-1.4562</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6805</v>
+        <v>2.7316</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.6293</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>4.3098</v>
+        <v>4.0974</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4827</v>
+        <v>-0.8479</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.2978</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4011</v>
+        <v>-0.5501</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1441</v>
+        <v>1.9837</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2534</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1093</v>
+        <v>0.3495</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6449</v>
+        <v>3.3192</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3077</v>
+        <v>0.3643</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6627999999999999</v>
+        <v>2.9549</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.3689</v>
+        <v>1.605</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1957</v>
+        <v>1.8644</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1732</v>
+        <v>-0.2593</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1513</v>
+        <v>2.6505</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4422</v>
+        <v>3.1576</v>
       </c>
       <c r="L3" t="n">
-        <v>0.709</v>
+        <v>-0.5071</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.5202</v>
+        <v>-1.0455</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.638</v>
+        <v>-1.2932</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.8822</v>
+        <v>0.2477</v>
       </c>
       <c r="P3" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4952</v>
+        <v>-3.6421</v>
       </c>
       <c r="R3" t="n">
-        <v>4.083</v>
+        <v>4.325</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6033</v>
+        <v>-0.107</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2128</v>
+        <v>0.1087</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3904</v>
+        <v>-0.2157</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8227</v>
+        <v>1.1383</v>
       </c>
       <c r="W3" t="n">
-        <v>3.4387</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.616</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>J. JACKSON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4999</v>
+        <v>1.7464</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5114</v>
+        <v>3.7938</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9885</v>
+        <v>-2.0475</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5164</v>
+        <v>-0.3537</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2166</v>
+        <v>-0.2446</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.733</v>
+        <v>-0.1091</v>
       </c>
       <c r="J4" t="n">
-        <v>2.31</v>
+        <v>2.0089</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5718</v>
+        <v>1.0342</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7382</v>
+        <v>0.9747</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8265</v>
+        <v>-2.3626</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3552</v>
+        <v>-1.2788</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4712</v>
+        <v>-1.0838</v>
       </c>
       <c r="P4" t="n">
-        <v>2.722</v>
+        <v>3.1868</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>4.083</v>
+        <v>3.4145</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6852</v>
+        <v>-1.5226</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0767</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6085</v>
+        <v>-0.8115</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9795</v>
+        <v>0.4358</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639</v>
+        <v>2.7237</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3405</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. JACKSON</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0433</v>
+        <v>0.8656</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2885</v>
+        <v>2.1347</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2451</v>
+        <v>-1.2691</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.354</v>
+        <v>-1.3867</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2526</v>
+        <v>-1.2248</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1014</v>
+        <v>-0.1619</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0357</v>
+        <v>1.1062</v>
       </c>
       <c r="K5" t="n">
-        <v>1.039</v>
+        <v>0.3987</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9967</v>
+        <v>0.7075</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.3897</v>
+        <v>-2.4929</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2917</v>
+        <v>-1.6235</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0981</v>
+        <v>-0.8694</v>
       </c>
       <c r="P5" t="n">
-        <v>3.1757</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4025</v>
+        <v>4.0974</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.2154</v>
+        <v>-0.1639</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2521</v>
+        <v>0.1063</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9633</v>
+        <v>-0.2702</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4371</v>
+        <v>0.8228</v>
       </c>
       <c r="W5" t="n">
-        <v>2.7317</v>
+        <v>3.4262</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.2946</v>
+        <v>-2.6034</v>
       </c>
     </row>
     <row r="6">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6328</v>
+        <v>-0.1794</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2624</v>
+        <v>0.0861</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3704</v>
+        <v>-0.2654</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9222</v>
+        <v>-0.9192</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3492</v>
+        <v>-0.3503</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.5688</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0537</v>
+        <v>-0.0602</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1283</v>
+        <v>-0.1346</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8685</v>
+        <v>-0.859</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3911</v>
+        <v>0.0569</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2087</v>
+        <v>0.1462</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1824</v>
+        <v>-0.0893</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0606</v>
+        <v>-1.0896</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5396</v>
+        <v>-0.8646</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.521</v>
+        <v>-0.225</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.2407</v>
+        <v>-3.241</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.5237</v>
+        <v>-2.5245</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.717</v>
+        <v>-0.7165</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1562</v>
+        <v>0.1269</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6967</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8529</v>
+        <v>0.8411</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.3969</v>
+        <v>-3.3679</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.827</v>
+        <v>-1.8103</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.5699</v>
+        <v>-1.5576</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>3.8562</v>
+        <v>3.8697</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8172</v>
+        <v>0.7872</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7047</v>
+        <v>0.4246</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1125</v>
+        <v>0.3627</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="W7" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3441</v>
+        <v>-1.3456</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1588</v>
+        <v>-0.1666</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1853</v>
+        <v>-1.1789</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.205</v>
+        <v>-1.2062</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6262</v>
+        <v>0.6261</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8312</v>
+        <v>-1.8323</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1195</v>
+        <v>0.1122</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3245</v>
+        <v>-1.3184</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1195</v>
+        <v>-1.1171</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5928</v>
+        <v>-0.5947</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3145</v>
+        <v>-0.3159</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5163</v>
+        <v>-2.2069</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2443</v>
+        <v>-0.8683</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2721</v>
+        <v>-1.3386</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.0763</v>
+        <v>-3.0869</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.616</v>
+        <v>-0.6229</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.4603</v>
+        <v>-2.464</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6943</v>
+        <v>-0.7227</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4707</v>
+        <v>0.4547</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1649</v>
+        <v>-1.1773</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3821</v>
+        <v>-2.3642</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2954</v>
+        <v>-1.2866</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2651</v>
+        <v>0.5841</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8771</v>
+        <v>0.29</v>
       </c>
       <c r="U9" t="n">
-        <v>0.388</v>
+        <v>0.294</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3948</v>
+        <v>-2.9064</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5797</v>
+        <v>-1.2394</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8151</v>
+        <v>-1.667</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6915</v>
+        <v>-2.6858</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5267</v>
+        <v>-1.5224</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1648</v>
+        <v>-1.1633</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0051</v>
+        <v>-0.0057</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.44</v>
+        <v>-0.4449</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.6966</v>
+        <v>-2.68</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6099</v>
+        <v>-1.6025</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9962</v>
+        <v>-0.5181</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4506</v>
+        <v>-0.0955</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5456</v>
+        <v>-0.4226</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4714</v>
+        <v>-3.4085</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1119</v>
+        <v>-2.1197</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3595</v>
+        <v>-1.2888</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0595</v>
+        <v>-1.0578</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0014</v>
+        <v>0.0028</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0609</v>
+        <v>-1.0606</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2904</v>
+        <v>-0.2854</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6388</v>
+        <v>-0.5783</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2087</v>
+        <v>-0.2091</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4301</v>
+        <v>-0.3692</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8598</v>
+        <v>-3.9263</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1135</v>
+        <v>-2.0127</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7463</v>
+        <v>-1.9136</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.6173999999999999</v>
+        <v>-0.6165</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6521</v>
+        <v>-0.6601</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0347</v>
+        <v>0.0436</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3352</v>
+        <v>-0.3472</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4471</v>
+        <v>-0.4589</v>
       </c>
       <c r="L12" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2822</v>
+        <v>-0.2694</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R12" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9479</v>
+        <v>-1.0219</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4174</v>
+        <v>-0.2998</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5305</v>
+        <v>-0.7221</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.2946</v>
+        <v>-2.2879</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.2946</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="13">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.134100000000003</v>
+        <v>-5.791300000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>1.325800000000001</v>
+        <v>1.3438</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.459799999999999</v>
+        <v>-7.1349</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.4362</v>
+        <v>-13.4759</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.400200000000001</v>
+        <v>-4.449000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-9.036099999999999</v>
+        <v>-9.0266</v>
       </c>
       <c r="J13" t="n">
-        <v>6.611499999999999</v>
+        <v>6.3621</v>
       </c>
       <c r="K13" t="n">
-        <v>5.839300000000001</v>
+        <v>5.681</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7723000000000001</v>
+        <v>0.6811999999999998</v>
       </c>
       <c r="M13" t="n">
-        <v>-20.0478</v>
+        <v>-19.838</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.2396</v>
+        <v>-10.1298</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.808299999999999</v>
+        <v>-9.7079</v>
       </c>
       <c r="P13" t="n">
-        <v>11.3417</v>
+        <v>11.3816</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7442</v>
+        <v>-14.7961</v>
       </c>
       <c r="R13" t="n">
-        <v>26.0859</v>
+        <v>26.1778</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.2645</v>
+        <v>-3.9262</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1794</v>
+        <v>-0.8164000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.0851</v>
+        <v>-3.109900000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2248999999999999</v>
+        <v>0.2291999999999992</v>
       </c>
       <c r="W13" t="n">
-        <v>10.6377</v>
+        <v>10.5941</v>
       </c>
       <c r="X13" t="n">
-        <v>-10.4128</v>
+        <v>-10.3649</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. TOMIC</t>
+          <t>C. HUNT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0858</v>
+        <v>6.2725</v>
       </c>
       <c r="E14" t="n">
-        <v>5.0979</v>
+        <v>7.5692</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9879</v>
+        <v>-1.2967</v>
       </c>
       <c r="G14" t="n">
-        <v>7.2243</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1718</v>
+        <v>1.0939</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0525</v>
+        <v>7.6861</v>
       </c>
       <c r="J14" t="n">
-        <v>7.0681</v>
+        <v>10.7711</v>
       </c>
       <c r="K14" t="n">
-        <v>5.7247</v>
+        <v>2.8473</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3434</v>
+        <v>7.9238</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1562</v>
+        <v>-1.9911</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.553</v>
+        <v>-1.7535</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7091</v>
+        <v>-0.2377</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.8147</v>
+        <v>-5.9184</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.6293</v>
+        <v>-8.194699999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>2.2763</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5464</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0162</v>
+        <v>0.0902</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5302</v>
+        <v>-0.1656</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.8703</v>
+        <v>3.4863</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6429</v>
+        <v>4.9026</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.5131</v>
+        <v>-1.4163</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. HUNT</t>
+          <t>A. TOMIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4637</v>
+        <v>5.5975</v>
       </c>
       <c r="E15" t="n">
-        <v>7.534</v>
+        <v>4.6872</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0704</v>
+        <v>0.9103</v>
       </c>
       <c r="G15" t="n">
-        <v>8.7791</v>
+        <v>7.221</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0864</v>
+        <v>5.159</v>
       </c>
       <c r="I15" t="n">
-        <v>7.6927</v>
+        <v>2.0621</v>
       </c>
       <c r="J15" t="n">
-        <v>10.8132</v>
+        <v>7.0319</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8675</v>
+        <v>5.6914</v>
       </c>
       <c r="L15" t="n">
-        <v>7.9458</v>
+        <v>1.3405</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0341</v>
+        <v>0.1891</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.781</v>
+        <v>-0.5325</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2531</v>
+        <v>0.7215</v>
       </c>
       <c r="P15" t="n">
-        <v>-5.8976</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q15" t="n">
-        <v>-8.166</v>
+        <v>-3.6421</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2683</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9143</v>
+        <v>2.0723</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0302</v>
+        <v>0.6663</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8841</v>
+        <v>1.406</v>
       </c>
       <c r="V15" t="n">
-        <v>3.4965</v>
+        <v>-1.8747</v>
       </c>
       <c r="W15" t="n">
-        <v>4.917</v>
+        <v>0.6311</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4205</v>
+        <v>-2.5058</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1105</v>
+        <v>3.3956</v>
       </c>
       <c r="E16" t="n">
-        <v>1.764</v>
+        <v>2.3315</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3465</v>
+        <v>1.0641</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0687</v>
+        <v>2.0779</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9465</v>
+        <v>0.9532</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1222</v>
+        <v>1.1248</v>
       </c>
       <c r="J16" t="n">
-        <v>2.289</v>
+        <v>2.276</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2468</v>
+        <v>1.2411</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0422</v>
+        <v>1.035</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2203</v>
+        <v>-0.1981</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3003</v>
+        <v>-0.2879</v>
       </c>
       <c r="O16" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8837</v>
+        <v>0.3973</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4174</v>
+        <v>0.174</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4664</v>
+        <v>0.2232</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9256</v>
+        <v>0.9204</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3278</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. KRAAG</t>
+          <t>A. HANGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7673</v>
+        <v>2.7157</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2011</v>
+        <v>0.7593</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5662</v>
+        <v>1.9564</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9795</v>
+        <v>-1.3589</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9814000000000001</v>
+        <v>-1.0058</v>
       </c>
       <c r="I17" t="n">
-        <v>3.9609</v>
+        <v>-0.3531</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6584</v>
+        <v>-1.2754</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3188</v>
+        <v>-0.3587</v>
       </c>
       <c r="L17" t="n">
-        <v>2.9772</v>
+        <v>-0.9167</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3211</v>
+        <v>-0.0835</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9837</v>
+        <v>0.5636</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1175</v>
+        <v>0.1835</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8771</v>
+        <v>0.0834</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2404</v>
+        <v>0.1002</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.1956</v>
+        <v>2.07</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.3563</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. HANGA</t>
+          <t>Y. KRAAG</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2453</v>
+        <v>1.3383</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.5755</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1701</v>
+        <v>0.7627</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3679</v>
+        <v>2.9771</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.016</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3519</v>
+        <v>3.9484</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2572</v>
+        <v>2.6317</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3534</v>
+        <v>-0.3242</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.9036999999999999</v>
+        <v>2.9559</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1107</v>
+        <v>0.3454</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.9925</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8147</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2775</v>
+        <v>0.6864</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6261</v>
+        <v>0.29</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6515</v>
+        <v>0.3964</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0761</v>
+        <v>-1.1871</v>
       </c>
       <c r="W18" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1093</v>
+        <v>-1.3449</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1421</v>
+        <v>0.0128</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5774</v>
+        <v>0.6933</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7195</v>
+        <v>-0.6805</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1811</v>
+        <v>-0.1764</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3333</v>
+        <v>0.3359</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5144</v>
+        <v>-0.5123</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6288</v>
+        <v>0.6261</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5541</v>
+        <v>0.5516</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8099</v>
+        <v>-0.8025</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1878</v>
+        <v>-0.0384</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0514</v>
+        <v>0.0673</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.839</v>
+        <v>-0.8171</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7906</v>
+        <v>-0.9198</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0484</v>
+        <v>0.1027</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3943</v>
+        <v>-1.3815</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2268</v>
+        <v>-0.2106</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1675</v>
+        <v>-1.171</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1827</v>
+        <v>-0.1926</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2116</v>
+        <v>-1.189</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3285</v>
+        <v>0.3368</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5263</v>
+        <v>0.4109</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1978</v>
+        <v>-0.0741</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1367</v>
+        <v>-1.366</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4185</v>
+        <v>-0.67</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.696</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7064</v>
+        <v>-0.704</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1702</v>
+        <v>1.1744</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8765</v>
+        <v>-1.8785</v>
       </c>
       <c r="J21" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0548</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7749</v>
+        <v>-0.7588</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3428</v>
+        <v>1.1104</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6472</v>
+        <v>0.4133</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6956</v>
+        <v>0.697</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2221</v>
+        <v>-1.9008</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.648</v>
+        <v>-2.3065</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4259</v>
+        <v>0.4057</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.799</v>
+        <v>-1.7998</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.9086</v>
+        <v>-1.9144</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2636</v>
+        <v>-0.2578</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3732</v>
+        <v>-0.3724</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0305</v>
+        <v>0.3542</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1391</v>
+        <v>0.2159</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1697</v>
+        <v>0.1383</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.582</v>
+        <v>-1.9762</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8735</v>
+        <v>-3.6827</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2915</v>
+        <v>1.7065</v>
       </c>
       <c r="G23" t="n">
         <v>0.3531</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3506</v>
+        <v>-0.3531</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7037</v>
+        <v>0.7062</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5542</v>
+        <v>0.5219</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1865</v>
+        <v>0.1649</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3678</v>
+        <v>0.357</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.2011</v>
+        <v>-0.1689</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5371</v>
+        <v>-0.518</v>
       </c>
       <c r="O23" t="n">
-        <v>0.336</v>
+        <v>0.3492</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0054</v>
+        <v>0.6203</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1089</v>
+        <v>0.348</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1035</v>
+        <v>0.2722</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2185</v>
+        <v>-0.2179</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2185</v>
+        <v>-0.2179</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6165</v>
+        <v>-5.5532</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1519</v>
+        <v>-2.9914</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4646</v>
+        <v>-2.5618</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5197</v>
+        <v>-2.5127</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8427</v>
+        <v>-1.8411</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.677</v>
+        <v>-0.6716</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0571</v>
+        <v>-1.0656</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2437</v>
+        <v>-1.2518</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4626</v>
+        <v>-1.4471</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8636</v>
+        <v>-0.8578</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>1.1565</v>
+        <v>0.2067</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1735</v>
+        <v>0.3505</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0169</v>
+        <v>-0.1438</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.134199999999998</v>
+        <v>7.719099999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>6.3672</v>
+        <v>6.045599999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.2329999999999997</v>
+        <v>1.6734</v>
       </c>
       <c r="G25" t="n">
-        <v>13.4363</v>
+        <v>13.4758</v>
       </c>
       <c r="H25" t="n">
-        <v>4.400300000000001</v>
+        <v>4.4491</v>
       </c>
       <c r="I25" t="n">
-        <v>9.036100000000001</v>
+        <v>9.0267</v>
       </c>
       <c r="J25" t="n">
-        <v>20.0478</v>
+        <v>19.8379</v>
       </c>
       <c r="K25" t="n">
-        <v>10.2395</v>
+        <v>10.1302</v>
       </c>
       <c r="L25" t="n">
-        <v>9.808500000000002</v>
+        <v>9.707899999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-6.6115</v>
+        <v>-6.362299999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-5.839299999999999</v>
+        <v>-5.681099999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7723</v>
+        <v>-0.6812999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-11.3417</v>
+        <v>-11.3817</v>
       </c>
       <c r="Q25" t="n">
-        <v>-26.0859</v>
+        <v>-26.1776</v>
       </c>
       <c r="R25" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2643</v>
+        <v>5.8541</v>
       </c>
       <c r="T25" t="n">
-        <v>3.085</v>
+        <v>3.1098</v>
       </c>
       <c r="U25" t="n">
-        <v>1.1793</v>
+        <v>2.7441</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.2250000000000001</v>
+        <v>-0.229200000000001</v>
       </c>
       <c r="W25" t="n">
-        <v>9.32</v>
+        <v>9.275399999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.545</v>
+        <v>-9.5046</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104589_W15.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104589_W15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.3495</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.6034</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-10.3649</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.4163</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-2.5058</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.3449</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.2179</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104589_W15.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-9.5046</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
